--- a/artfynd/A 45071-2024 artfynd.xlsx
+++ b/artfynd/A 45071-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120488857</v>
+        <v>120488855</v>
       </c>
       <c r="B2" t="n">
-        <v>89236</v>
+        <v>86282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>245042</v>
+        <v>3712</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695983</v>
+        <v>696003</v>
       </c>
       <c r="R2" t="n">
-        <v>6356164</v>
+        <v>6356148</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120488855</v>
+        <v>120488857</v>
       </c>
       <c r="B4" t="n">
-        <v>86282</v>
+        <v>89236</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3712</v>
+        <v>245042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696003</v>
+        <v>695983</v>
       </c>
       <c r="R4" t="n">
-        <v>6356148</v>
+        <v>6356164</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120488854</v>
+        <v>120488089</v>
       </c>
       <c r="B5" t="n">
-        <v>86367</v>
+        <v>86449</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,50 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Magnuse, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696042</v>
+        <v>696027</v>
       </c>
       <c r="R5" t="n">
-        <v>6356117</v>
+        <v>6356059</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1126,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120488089</v>
+        <v>120488854</v>
       </c>
       <c r="B6" t="n">
-        <v>86449</v>
+        <v>86367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,41 +1129,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Magnuse, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696027</v>
+        <v>696042</v>
       </c>
       <c r="R6" t="n">
-        <v>6356059</v>
+        <v>6356117</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,12 +1216,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 45071-2024 artfynd.xlsx
+++ b/artfynd/A 45071-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120488855</v>
+        <v>120488857</v>
       </c>
       <c r="B2" t="n">
-        <v>86282</v>
+        <v>89236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3712</v>
+        <v>245042</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696003</v>
+        <v>695983</v>
       </c>
       <c r="R2" t="n">
-        <v>6356148</v>
+        <v>6356164</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120488857</v>
+        <v>120488089</v>
       </c>
       <c r="B4" t="n">
-        <v>89236</v>
+        <v>86449</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,50 +908,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>245042</v>
+        <v>6003295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Magnuse, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>695983</v>
+        <v>696027</v>
       </c>
       <c r="R4" t="n">
-        <v>6356164</v>
+        <v>6356059</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,12 +986,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1011,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120488089</v>
+        <v>120488855</v>
       </c>
       <c r="B5" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1014,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Magnuse, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696027</v>
+        <v>696003</v>
       </c>
       <c r="R5" t="n">
-        <v>6356059</v>
+        <v>6356148</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 45071-2024 artfynd.xlsx
+++ b/artfynd/A 45071-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120488857</v>
+        <v>120488089</v>
       </c>
       <c r="B2" t="n">
-        <v>89236</v>
+        <v>86449</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>245042</v>
+        <v>6003295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Magnuse, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695983</v>
+        <v>696027</v>
       </c>
       <c r="R2" t="n">
-        <v>6356164</v>
+        <v>6356059</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120488085</v>
+        <v>120488857</v>
       </c>
       <c r="B3" t="n">
-        <v>86465</v>
+        <v>89236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,41 +793,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>248947</v>
+        <v>245042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Magnuse, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>695931</v>
+        <v>695983</v>
       </c>
       <c r="R3" t="n">
-        <v>6356260</v>
+        <v>6356164</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,12 +880,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120488089</v>
+        <v>120488854</v>
       </c>
       <c r="B4" t="n">
-        <v>86449</v>
+        <v>86367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,41 +908,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Magnuse, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696027</v>
+        <v>696042</v>
       </c>
       <c r="R4" t="n">
-        <v>6356059</v>
+        <v>6356117</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +995,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1002,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120488855</v>
+        <v>120488085</v>
       </c>
       <c r="B5" t="n">
-        <v>86282</v>
+        <v>86465</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,50 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>248947</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Magnuse, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696003</v>
+        <v>695931</v>
       </c>
       <c r="R5" t="n">
-        <v>6356148</v>
+        <v>6356260</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120488854</v>
+        <v>120488855</v>
       </c>
       <c r="B6" t="n">
-        <v>86367</v>
+        <v>86282</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,25 +1129,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>449</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696042</v>
+        <v>696003</v>
       </c>
       <c r="R6" t="n">
-        <v>6356117</v>
+        <v>6356148</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
